--- a/artfynd/A 37786-2022 artfynd.xlsx
+++ b/artfynd/A 37786-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37786-2022 artfynd.xlsx
+++ b/artfynd/A 37786-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>90851150</v>
       </c>
       <c r="B2" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539371.8819335557</v>
+        <v>539372</v>
       </c>
       <c r="R2" t="n">
-        <v>7126500.15747336</v>
+        <v>7126500</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-09-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90900710</v>
+        <v>90921586</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>219795</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539360.9754916332</v>
+        <v>539367</v>
       </c>
       <c r="R3" t="n">
-        <v>7126536.102393922</v>
+        <v>7126557</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,21 +854,11 @@
           <t>2019-09-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +870,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Naturskog</t>
+          <t>Högörtsstråk</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91132747</v>
+        <v>90900710</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,14 +928,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Ång</t>
+          <t>Bäckernacken-Brattbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539357.2138749658</v>
+        <v>539361</v>
       </c>
       <c r="R4" t="n">
-        <v>7126523.881398256</v>
+        <v>7126536</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,19 +965,9 @@
           <t>2019-09-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91132750</v>
+        <v>90921585</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,14 +1039,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Ång</t>
+          <t>Bäckernacken-Brattbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539372.1692617956</v>
+        <v>539367</v>
       </c>
       <c r="R5" t="n">
-        <v>7126545.809820265</v>
+        <v>7126557</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,21 +1076,11 @@
           <t>2019-09-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-09-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1152,7 +1092,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Naturskog</t>
+          <t>Högörtsstråk</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1172,6 +1112,228 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>91132747</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Halbodarna_SÖ, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>539357</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7126524</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-09-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-09-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Naturskog</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>91132750</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Halbodarna_SÖ, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>539372</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7126546</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-09-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-09-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Naturskog</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>

--- a/artfynd/A 37786-2022 artfynd.xlsx
+++ b/artfynd/A 37786-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90851150</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921586</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90900710</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921585</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132747</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,8 +1368,21 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132750</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>